--- a/etf_holdings/2026-09-30_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-30_common_holdings_all.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="AA2" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>107.22%</t>
+          <t>107.23%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="AA3" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>71.20%</t>
+          <t>70.97%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="AA4" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>56.63%</t>
+          <t>56.59%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="AA5" t="n">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>54.68%</t>
+          <t>54.62%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>4.56%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
